--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0007.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0007.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhìn vào sắc xanh thẳm nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhìn vào sắc xanh thẳm nhất của Ragunna.
 Có thể nhận sau khi bắt đầu Nhiệm Vụ Phụ "Dấu vết Thủy Triều."</t>
         </is>
       </c>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"Tiến lên, các hiệp sĩ! Lâu đài Porto-Veno sẽ ghi danh chiến công của các ngươi."</t>
+          <t>"Tiến lên, các hiệp sĩ! Porto-Veno Castle sẽ ghi danh chiến công của các ngươi."</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Bước vào đêm tĩnh mịch nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; Bước vào đêm tĩnh mịch nhất của Ragunna.
 Có thể nhận sau khi hoàn thành Dấu Vết Thủy Triều I.</t>
         </is>
       </c>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Xoa dịu mặt nước tĩnh lặng nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; Xoa dịu mặt nước tĩnh lặng nhất của Ragunna.
 Có thể nhận sau khi hoàn thành Dấu Vết Thủy Triều I.</t>
         </is>
       </c>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Phản chiếu ngọn gió lặng im của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Phản chiếu ngọn gió lặng im của Ragunna.
 Nhận được sau khi hoàn thành Dấu Vết Thủy Triều I.</t>
         </is>
       </c>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Chiêm ngưỡng tảng đá vững chãi của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Chiêm ngưỡng tảng đá vững chãi của Ragunna.
 Có thể nhận sau khi hoàn thành Dấu vết Thủy Triều I.</t>
         </is>
       </c>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Vuốt ve đám mây mềm nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Vuốt ve đám mây mềm nhất của Ragunna.
 Có thể nhận sau khi hoàn thành Dấu Vết Thủy Triều I.</t>
         </is>
       </c>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>"&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Hãy nhớ đến linh hồn thân yêu nhất của Ragunna.
+          <t>"&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Hãy nhớ đến linh hồn thân yêu nhất của Ragunna.
 Có thể nhận sau khi hoàn thành Dấu vết thủy triều I-VI.</t>
         </is>
       </c>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Hãy nuôi dưỡng cây cổ thụ lâu đời nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Hãy nuôi dưỡng cây cổ thụ lâu đời nhất của Ragunna.
 Mở khóa sau khi khám phá bí mật trong sâu thẳm Oakheart Highcourt.</t>
         </is>
       </c>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Vượt qua biển động dữ dội nhất của Ragunna.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Vượt qua biển động dữ dội nhất của Ragunna.
 Mở khóa sau khi hoàn thành Nhiệm vụ Khám phá "Nơi Gió Trở Về Cõi Trời".</t>
         </is>
       </c>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Ta từng phỏng vấn một nghệ sĩ ở Ragunna, ông ấy nói: "Tiền sinh ra để kiếm, không phải để dành."</t>
+          <t>Tao từng phỏng vấn một nghệ sĩ ở Ragunna, ông ấy nói: "Tiền sinh ra để kiếm, không phải để dành."</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cậu nghĩ Cộng Hưởng Giả nên được tự do sử dụng Thiết bị đầu cuối của riêng mình không?</t>
+          <t>Cậu nghĩ Resonator nên được tự do sử dụng Thiết bị đầu cuối của riêng mình không?</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Ta hiểu... nhưng ta nghĩ hầu hết Cộng Hưởng Giả đều muốn có Thiết bị đầu cuối riêng của mình hơn.</t>
+          <t>Ta hiểu... nhưng ta nghĩ hầu hết Resonator đều muốn có Thiết bị đầu cuối riêng của mình hơn.</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Thiết bị đầu cuối là vật bất ly thân của Cộng Hưởng Giả và cần được phép sử dụng.</t>
+          <t>Thiết bị đầu cuối là vật bất ly thân của Resonator và cần được phép sử dụng.</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tiếng vọng dường như đã trở thành một phần không thể thiếu trong cuộc sống của người Ragunnesi.</t>
+          <t>Echo dường như đã trở thành một phần không thể thiếu trong cuộc sống của người Ragunnesi.</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{0} Unlocked</t>
+          <t>{0} Đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả Thử Nghiệm đã hết hạn. Vui lòng thay thế</t>
+          <t>Resonator Thử Nghiệm đã hết hạn. Vui lòng thay thế</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Đang có Cộng Hưởng Giả Thử Nghiệm. Không thể vào Dungeon</t>
+          <t>Đang có Resonator Thử Nghiệm. Không thể vào Dungeon</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả có thể Trượt Tường trên các bức tường và vách đá dốc như trên mặt đất.</t>
+          <t>Resonator có thể Trượt Tường trên các bức tường và vách đá dốc như trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{0} Unlocked</t>
+          <t>{0} Đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>{0}phút</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>&lt;color=#e1ac68&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;color=#36cd33&gt;Tất cả stage rewards have been claimed&lt;/color&gt;</t>
+          <t>&lt;color=#36cd33&gt;Đã nhận tất cả phần thưởng giai đoạn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=#c15757&gt;Complete the previous stage to unlock&lt;/color&gt;</t>
+          <t>&lt;color=#c15757&gt;Hoàn thành giai đoạn trước để mở khóa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cực mạnh xuất hiện tại Sonoro, vùng Cao nguyên Desorock. Có khả năng sử dụng sức mạnh Electro.</t>
+          <t>Một Tacet Discord cực mạnh xuất hiện tại Sonoro, vùng Desorock Highlands. Có khả năng sử dụng sức mạnh Electro.</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Panhua's Restaurant&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhà Hàng Panhua&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Waveplates Exchange&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Sàn Giao Dịch Waveplate&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Weapon Shop&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Vũ Khí&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Mahe's Grocery&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Tạp Hóa Mahe&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Weapon Shop&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Vũ Khí&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Huaxu Academy&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Học Viện Huaxu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Shifang Pharmacy&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Dược Phẩm Shifang&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Solis Tavern&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Quán Rượu Solis&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;The Silver Helmet&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Mũ Bạc&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Steward's Supply Station&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Trạm Cung Ứng Quản Gia&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Souvenir Cửa hàng&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cửa Hàng Lưu Niệm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Relic Merchant&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Thương Nhân Di Vật&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Panhua's Restaurant&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhà Hàng Panhua&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Pioneer Association&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Hiệp Hội Tiên Phong&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Cooking&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nấu Ăn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Averardo Bank Teller&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Nhân Viên Ngân Hàng Averardo&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Chiêu mộ Cộng Hưởng Giả để mở khóa.</t>
+          <t>Chiêu mộ Resonator để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Hello!</t>
+          <t>Chào cậu!</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Để đồ lại đây. Ta đi nghỉ một lát.</t>
+          <t>Để đồ lại đây. Tao đi nghỉ một lát.</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Trả lại đây cho ta. Đổi lại, ta sẽ dạy ngươi cách săn mồi.</t>
+          <t>Trả lại đây cho tao. Đổi lại, tao sẽ dạy mày cách săn mồi.</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Cái két sắt đó ta lấy luôn!</t>
+          <t>Cái két sắt đó tao lấy luôn!</t>
         </is>
       </c>
     </row>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Tham gia quay thưởng để có cơ hội thăng cấp một Cộng Hưởng Giả.</t>
+          <t>Tham gia quay thưởng để có cơ hội thăng cấp một Resonator.</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tiêu 100 Mảnh Giấc Mơ để có cơ hội thăng cấp một Cộng Hưởng Giả.</t>
+          <t>Tiêu 100 Mảnh Giấc Mơ để có cơ hội thăng cấp một Resonator.</t>
         </is>
       </c>
     </row>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Dùng 200 Mảnh Giấc Mơ để có cơ hội thăng cấp Cộng Hưởng Giả một lần</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để có cơ hội thăng cấp Resonator một lần</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dùng 600 Mảnh Giấc Mơ để thăng cấp Cộng Hưởng Giả hai lần.</t>
+          <t>Dùng 600 Mảnh Giấc Mơ để thăng cấp Resonator hai lần.</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Dùng 400 Mảnh Giấc Mơ để thăng tiến Cộng Hưởng Giả hai lần</t>
+          <t>Dùng 400 Mảnh Giấc Mơ để thăng tiến Resonator hai lần</t>
         </is>
       </c>
     </row>
@@ -23348,7 +23348,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tham gia quay thưởng để có cơ hội thăng cấp một Cộng Hưởng Giả.</t>
+          <t>Tham gia quay thưởng để có cơ hội thăng cấp một Resonator.</t>
         </is>
       </c>
     </row>
@@ -23478,7 +23478,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tiêu 100 Mảnh Giấc Mơ để có cơ hội thăng cấp một Cộng Hưởng Giả.</t>
+          <t>Tiêu 100 Mảnh Giấc Mơ để có cơ hội thăng cấp một Resonator.</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Dùng 200 Mảnh Giấc Mơ để có cơ hội thăng cấp Cộng Hưởng Giả một lần</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để có cơ hội thăng cấp Resonator một lần</t>
         </is>
       </c>
     </row>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -24453,7 +24453,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Làm Mới ({0}/{1})</t>
+          <t>Làm mới ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>&lt;color=#aaaaaa&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -25493,7 +25493,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Một Discord mạnh mẽ xuất hiện tại Tacet Field ở Desorock Highlands, có khả năng sử dụng sức mạnh của Electro.</t>
+          <t>Một Tacet Discord mạnh mẽ xuất hiện tại Tổ Tacet của Desorock Highlands và có khả năng sử dụng sức mạnh của Electro.</t>
         </is>
       </c>
     </row>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Thế giới của Wuthering Waves còn vô vàn điều bí ẩn chờ Rover khám phá...</t>
+          <t>Thế giới của Wuthering Waves còn vô vàn điều bí ẩn chờ Vận Mệnh Giả khám phá...</t>
         </is>
       </c>
     </row>
@@ -28615,7 +28615,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>&lt;color=#f7eba6&gt;Substat Slot&lt;/color&gt;</t>
+          <t>&lt;color=#f7eba6&gt;Ô Thuộc Tính Phụ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29070,7 +29070,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt; Tiếng Vang. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
+          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt; Echo. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nâng Cấp Liên Minh và nhận thưởng từ &lt;color=#c19f51&gt;Level Bundle&lt;/color&gt;</t>
+          <t>Nâng Cấp Liên Minh và nhận thưởng từ &lt;color=#c19f51&gt;Gói Cấp Độ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29655,7 +29655,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Đăng nhập 5 ngày trong &lt;color=#c19f51&gt;Gifts of Thawing Frost&lt;/color&gt;</t>
+          <t>Đăng nhập 5 ngày trong &lt;color=#c19f51&gt;Quà Tặng Sương Tan&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Hoàn thành &lt;color=#c19f51&gt;Tower of Adversity&lt;/color&gt;: Khu Vực Ổn Định</t>
+          <t>Hoàn thành &lt;color=#c19f51&gt;Tháp Nghịch Cảnh&lt;/color&gt;: Khu Vực Ổn Định</t>
         </is>
       </c>
     </row>
@@ -29785,7 +29785,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm &lt;color=#c19f51&gt;"We Promise, We Deliver: Port City of Guixu"&lt;/color&gt;</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm &lt;color=#c19f51&gt;"Lời Hứa, Ta Sẽ Giao Hàng: Thành Phố Cảng Guixu"&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29850,7 +29850,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai Đoạn 5 trong &lt;color=#c19f51&gt;Milestones&lt;/color&gt;</t>
+          <t>Hoàn thành Giai Đoạn 5 trong &lt;color=#c19f51&gt;Cột Mốc&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Gần đây, Khu Huấn Luyện Mô Phỏng đang cung cấp phần thưởng huấn luyện hấp dẫn hơn cho Cộng Hưởng Giả. Hãy dùng Waveplates để nhận thêm phần thưởng từ Thử Thách Mô Phỏng!</t>
+          <t>Gần đây, Khu Huấn Luyện Mô Phỏng đang cung cấp phần thưởng huấn luyện hấp dẫn hơn cho Resonator. Hãy dùng Waveplates để nhận thêm phần thưởng từ Thử Thách Mô Phỏng!</t>
         </is>
       </c>
     </row>
@@ -30175,7 +30175,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả mới đã tham gia Huấn Luyện Mô Phỏng. Hãy tận dụng sức mạnh của họ để hoàn thành thử thách và thu thập dữ liệu liên quan để nhận thưởng.</t>
+          <t>Một Resonator mới đã tham gia Huấn Luyện Mô Phỏng. Hãy tận dụng sức mạnh của họ để hoàn thành thử thách và thu thập dữ liệu liên quan để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>&lt;color=#8c4646&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30760,7 +30760,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ta là Yinlin. Còn việc ta làm... Suỵt, đừng nói ra chỗ đông người.</t>
+          <t>Tao là Yinlin. Còn việc tao làm... Suỵt, đừng nói ra chỗ đông người.</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Outlaw Blue, Apollo Orange, Hazard Yellow, Acid Green... Đoán xem lần tới ta sẽ chọn màu gì?</t>
+          <t>Outlaw Blue, Apollo Orange, Hazard Yellow, Acid Green... Đoán xem lần tới tao sẽ chọn màu gì?</t>
         </is>
       </c>
     </row>
@@ -31735,7 +31735,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tiến sĩ Luuk Herssen, từ Đơn vị Điều dưỡng Cộng Hưởng Giả. Hiếm khi thấy cậu ngoài văn phòng đấy. À, cứ gọi mình là Luuk thôi.</t>
+          <t>Tiến sĩ Luuk Herssen, từ Đơn vị Điều dưỡng Resonator. Hiếm khi thấy cậu ngoài văn phòng đấy. À, cứ gọi mình là Luuk thôi.</t>
         </is>
       </c>
     </row>
@@ -31865,7 +31865,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Cộng Hưởng Giả có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
+          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Resonator có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -31930,7 +31930,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Cộng Hưởng Giả có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
+          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Resonator có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -31995,7 +31995,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sử dụng Súng Ngắn làm vũ khí có thể Chuyển Vào Chế Độ Nhắm.</t>
+          <t>Resonator sử dụng Súng Ngắn làm vũ khí có thể Chuyển Vào Chế Độ Nhắm.</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32060,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Có thể bung dù của Đôi Cánh Lướt Gió bằng cách nhấn nút Nhảy khi Cộng Hưởng Giả đang ở trên không.</t>
+          <t>Có thể bung dù của Đôi Cánh Lướt Gió bằng cách nhấn nút Nhảy khi Resonator đang ở trên không.</t>
         </is>
       </c>
     </row>
@@ -32125,7 +32125,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Trong nhiệm vụ hoặc khi chơi, Cộng Hưởng Giả thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
+          <t>Trong nhiệm vụ hoặc khi chơi, Resonator thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Cộng Hưởng Giả có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
+          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Resonator có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Cộng Hưởng Giả có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
+          <t>Giữ Dash khi áp sát tường đứng để Thực Hiện Dash Tường. Ở trạng thái này, Resonator có thể di chuyển tự do trên tường và vách đá dốc như trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -32320,7 +32320,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
+          <t>Resonator sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
+          <t>Resonator sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
+          <t>Resonator sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
         </is>
       </c>
     </row>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
+          <t>Resonator sử dụng Súng Ngắn có thể chuyển sang Chế Độ Nhắm Bắn.</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Trong nhiệm vụ hoặc khi chơi, Cộng Hưởng Giả thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
+          <t>Trong nhiệm vụ hoặc khi chơi, Resonator thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32775,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Trong nhiệm vụ hoặc khi chơi, Cộng Hưởng Giả thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
+          <t>Trong nhiệm vụ hoặc khi chơi, Resonator thử nghiệm có thể tạm thời gia nhập đội, do đó đội có thể có tối đa 4 thành viên cùng lúc.</t>
         </is>
       </c>
     </row>
